--- a/data/contratos/contratos_arp_identificados.xlsx
+++ b/data/contratos/contratos_arp_identificados.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos ARP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Contratos ARP" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25018799</t>
+          <t>57/2025/PGJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>20/2025</t>
+          <t>7/2024</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -509,135 +509,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Adesão nº 04/2025 à Ata de Registro de Preços nº 20/2025, oriunda do Pregão Eletrônico nº 60/2024 do Tribunal de Justiça</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>25018921</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ADESÃO (carona recebida)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>1/2025</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>pendente</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Adesão nº 07/2025 à Ata de Registro de Preços nº 01/2025/2025 decorrente do Pregão Eletrônico nº 001/2024, realizado pel</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>64/2025/FMMP/PI</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>ADESÃO (carona recebida)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>90022/2024</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>pendente</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Adesão à ata de registro de preços nº ARP25CIN000024, oriunda do Processo Administrativo Licitatório nº 0000154.02.01-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>109/2025 PGJ</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>ADESÃO (carona recebida)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>39/2024</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>pendente</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>ADESÃO nº 06/2025 à Ata de Registro de Preços nº nº 039/2024, oriunda do Pregão Eletrônico SGP-e nº PMSC/17517/2023 (Pol</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2025NE00141</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>ADESÃO (carona recebida)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>39/2024</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>pendente</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Adesão à Ata de Registro de Preços nº nº 039/2024, oriunda do Pregão Eletrônico SGP-e nº PMSC/17517/2023 (Polícia Milita</t>
+          <t>ADESÃO Nº 01/2025 À ATA DE REGISTRO DE PREÇOS N° 07/2024, ORIUNDA DO PREGÃO ELETRÔNICO N° 07/2024 DO INSTITUTO DE METROL</t>
         </is>
       </c>
     </row>
